--- a/Códigos_oficiales/codigos_optimizacion/optimizacion_pymoo/resultados_cv_pymoo_100k_v1.xlsx
+++ b/Códigos_oficiales/codigos_optimizacion/optimizacion_pymoo/resultados_cv_pymoo_100k_v1.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89FC7595-7981-4F1E-AEDD-2998F246C530}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="resultados" sheetId="1" r:id="rId1"/>
@@ -499,14 +499,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -917,89 +916,89 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="4">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2">
         <v>21355.620179099998</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2">
         <v>355.927002985</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" t="s">
         <v>31</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" t="s">
         <v>32</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I2">
         <v>0.4181831086608338</v>
       </c>
-      <c r="J2" s="4">
+      <c r="J2">
         <v>0.24043369167794559</v>
       </c>
-      <c r="K2" s="4">
+      <c r="K2">
         <v>0.65861680033877945</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" t="s">
         <v>33</v>
       </c>
-      <c r="M2" s="4">
+      <c r="M2">
         <v>1001</v>
       </c>
-      <c r="N2" s="4">
+      <c r="N2">
         <v>1.9032249638027111E-3</v>
       </c>
-      <c r="O2" s="4">
+      <c r="O2">
         <v>0.29541192861617471</v>
       </c>
-      <c r="P2" s="4">
+      <c r="P2">
         <v>1.0807120123571829</v>
       </c>
-      <c r="Q2" s="4">
+      <c r="Q2">
         <v>4.1534149641260703</v>
       </c>
-      <c r="R2" s="4">
+      <c r="R2">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="S2" s="4">
+      <c r="S2">
         <v>8.5518540000000005</v>
       </c>
-      <c r="T2" s="4">
+      <c r="T2">
         <v>7.1656500000000003</v>
       </c>
-      <c r="U2" s="4">
+      <c r="U2">
         <v>44.150669999999998</v>
       </c>
-      <c r="V2" s="4">
+      <c r="V2">
         <v>42.528283999999999</v>
       </c>
-      <c r="W2" s="4">
+      <c r="W2">
         <v>1E-4</v>
       </c>
-      <c r="X2" s="4">
+      <c r="X2">
         <v>1.745039102376857</v>
       </c>
-      <c r="Y2" s="4">
+      <c r="Y2">
         <v>7.3891878611952819</v>
       </c>
-      <c r="Z2" s="4">
+      <c r="Z2">
         <v>1.6426339999999999</v>
       </c>
-      <c r="AA2" s="4">
+      <c r="AA2">
         <v>0.16193672239923571</v>
       </c>
-      <c r="AB2" s="4">
+      <c r="AB2">
         <v>0.72451861909053172</v>
       </c>
     </row>
@@ -2293,89 +2292,89 @@
         <v>0.70531814315515684</v>
       </c>
     </row>
-    <row r="18" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
+    <row r="18" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" t="s">
         <v>109</v>
       </c>
-      <c r="C18" s="4">
+      <c r="C18">
         <v>21599.756506000009</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18">
         <v>359.99594176666682</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" t="s">
         <v>110</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" t="s">
         <v>111</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" t="s">
         <v>112</v>
       </c>
-      <c r="H18" s="4" t="s">
+      <c r="H18" t="s">
         <v>113</v>
       </c>
-      <c r="I18" s="4">
+      <c r="I18">
         <v>0.34733197304329849</v>
       </c>
-      <c r="J18" s="4">
+      <c r="J18">
         <v>0.22409851946676779</v>
       </c>
-      <c r="K18" s="4">
+      <c r="K18">
         <v>0.57143049251006639</v>
       </c>
-      <c r="L18" s="4" t="s">
+      <c r="L18" t="s">
         <v>33</v>
       </c>
-      <c r="M18" s="4">
+      <c r="M18">
         <v>1001</v>
       </c>
-      <c r="N18" s="4">
+      <c r="N18">
         <v>1.9473455526333599E-2</v>
       </c>
-      <c r="O18" s="4">
+      <c r="O18">
         <v>0.40363681922054673</v>
       </c>
-      <c r="P18" s="4">
+      <c r="P18">
         <v>0.80762974192179127</v>
       </c>
-      <c r="Q18" s="4">
+      <c r="Q18">
         <v>4.0271430284063969</v>
       </c>
-      <c r="R18" s="4">
+      <c r="R18">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="S18" s="4">
+      <c r="S18">
         <v>8.5518540000000005</v>
       </c>
-      <c r="T18" s="4">
+      <c r="T18">
         <v>7.1656500000000003</v>
       </c>
-      <c r="U18" s="4">
+      <c r="U18">
         <v>44.150669999999998</v>
       </c>
-      <c r="V18" s="4">
+      <c r="V18">
         <v>42.528283999999999</v>
       </c>
-      <c r="W18" s="4">
+      <c r="W18">
         <v>1E-4</v>
       </c>
-      <c r="X18" s="4">
+      <c r="X18">
         <v>2.383885966258056</v>
       </c>
-      <c r="Y18" s="4">
+      <c r="Y18">
         <v>2.7991870033666779</v>
       </c>
-      <c r="Z18" s="4">
+      <c r="Z18">
         <v>1.6426339999999999</v>
       </c>
-      <c r="AA18" s="4">
+      <c r="AA18">
         <v>0.21171360604458109</v>
       </c>
-      <c r="AB18" s="4">
+      <c r="AB18">
         <v>0.56681751349959086</v>
       </c>
     </row>
